--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260903.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260903.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.07%</t>
         </is>
       </c>
     </row>
@@ -638,205 +638,205 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.78%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>6,254,000</t>
+          <t>21,637,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>21,637,000</t>
+          <t>6,254,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>48,740,000</t>
+          <t>35,649,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>48,740,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>10,156,000</t>
+          <t>562,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>35,649,000</t>
+          <t>10,156,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,948,000</t>
+          <t>20,627,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11,407,000</t>
+          <t>3,948,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,627,000</t>
+          <t>11,407,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -858,112 +858,112 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>3,615,062,998</t>
+          <t>26,162,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>6,739,000</t>
+          <t>34,731,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>26,162,000</t>
+          <t>6,739,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>34,731,000</t>
+          <t>3,519,820,763</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>22,764,000</t>
+          <t>37,749,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,44 +975,44 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,588,000</t>
+          <t>22,764,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,304,000</t>
+          <t>9,588,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1166,24 +1166,24 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,213,000</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>15,213,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,659,761,747</t>
+          <t>2,632,081,747</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1276,95 +1276,95 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>4,984,000</t>
+          <t>6,179,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,179,000</t>
+          <t>4,984,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>7,883,000</t>
+          <t>9,652,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>9,652,000</t>
+          <t>7,883,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1408,51 +1408,51 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>14,405,000</t>
+          <t>10,241,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10,241,000</t>
+          <t>14,405,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1474,46 +1474,46 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>16,642,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,642,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1613,39 +1613,39 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>18,852,000</t>
+          <t>48,160,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>48,160,000</t>
+          <t>18,852,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>6,733,000</t>
+          <t>1,586,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,22 +1679,22 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,586,000</t>
+          <t>6,733,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1761,6 +1761,28 @@
       <c r="D73" s="4" t="inlineStr">
         <is>
           <t>0.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>PB_NTD</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>PAYABLES</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>-19,906,513</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
